--- a/data/trending_integrated_20261026_13.xlsx
+++ b/data/trending_integrated_20261026_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G2" t="n">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58947456895</v>
+        <v>58966480445</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -622,20 +622,20 @@
         <v>336000</v>
       </c>
       <c r="S2" t="n">
-        <v>305000</v>
+        <v>307000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 세력의 대차 상환 가능성 및 스퀴즈 랠리 기대. 글로벌 AI 신약 밸류체인 합류 및 빅파마와 후기 임상 진입 뉴스 기반 긍정적 전망.</t>
+          <t>공매도 세력에 대한 언급과 함께 차세대 면역항암제 관련 긍정적 뉴스 및 빅파마와의 임상 진입 소식이 사실 기반으로 제시됨. 연기금 순매수 등 객관적 지표와 함께 주가 상승 기대감이 높음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', 'AI 신약', '임상']</t>
+          <t>['면역항암제', 'AI 신약', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,184 +655,184 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>진양산업</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5850</v>
+        <v>2080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+7.00%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.67</v>
+        <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5490</v>
+        <v>1944</v>
       </c>
       <c r="K3" t="n">
-        <v>6250</v>
+        <v>2100</v>
       </c>
       <c r="L3" t="n">
-        <v>6340</v>
+        <v>2325</v>
       </c>
       <c r="M3" t="n">
-        <v>5470</v>
+        <v>2015</v>
       </c>
       <c r="N3" t="n">
-        <v>2.67</v>
+        <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>39508950040</v>
+        <v>63736636547</v>
       </c>
       <c r="P3" t="n">
-        <v>7400</v>
+        <v>4980</v>
       </c>
       <c r="Q3" t="n">
-        <v>3660</v>
+        <v>749</v>
       </c>
       <c r="R3" t="n">
-        <v>41000</v>
+        <v>-27000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급이 다수 있으나, 실제 주가 전망에 대한 구체적 근거 부족.</t>
+          <t>로봇 섹터 강세 및 신용/단타 투자자 퇴출 언급. 기술적 분석 기반 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치 테마주', '개미', '우상향']</t>
+          <t>['로봇 섹터', '단타', '기술적 분석']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>003780</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>진양산업</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2035</v>
+        <v>5870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.68%</t>
+          <t>'+6.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.13</v>
+        <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1944</v>
+        <v>5490</v>
       </c>
       <c r="K4" t="n">
-        <v>2100</v>
+        <v>6250</v>
       </c>
       <c r="L4" t="n">
-        <v>2325</v>
+        <v>6340</v>
       </c>
       <c r="M4" t="n">
-        <v>2020</v>
+        <v>5470</v>
       </c>
       <c r="N4" t="n">
-        <v>4.87</v>
+        <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>62044221790</v>
+        <v>39860399160</v>
       </c>
       <c r="P4" t="n">
-        <v>4980</v>
+        <v>7400</v>
       </c>
       <c r="Q4" t="n">
-        <v>749</v>
+        <v>3660</v>
       </c>
       <c r="R4" t="n">
-        <v>89000</v>
+        <v>-45000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 및 신용/단타 투자자 퇴출 언급. 기술적 분석 기반 긍정적 흐름 기대.</t>
+          <t>정치 테마주 관련 언급이 많으나, 특정 정치인 지지 및 당선 가능성 언급과 함께 주가 상승 기대감이 일부 나타남. 단기적인 주가 상승 전망만 존재하며, 객관적 근거는 부족함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '단타', '기술적 분석']</t>
+          <t>['정치 테마주', '주가 상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>003780</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1282000</v>
+        <v>1287000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.39%</t>
+          <t>'+0.78%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G5" t="n">
-        <v>1845</v>
+        <v>1852</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1948165278500</v>
+        <v>1985108567000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,10 +895,10 @@
         <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>-46000</v>
+        <v>-134000</v>
       </c>
       <c r="S5" t="n">
-        <v>30000</v>
+        <v>77000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59700</v>
+        <v>59800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.17%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>195030920850</v>
+        <v>201993936550</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -987,10 +987,10 @@
         <v>23150</v>
       </c>
       <c r="R6" t="n">
-        <v>352000</v>
+        <v>396000</v>
       </c>
       <c r="S6" t="n">
-        <v>16000</v>
+        <v>65000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213500</v>
+        <v>214000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>456</v>
       </c>
       <c r="G7" t="n">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1480569562750</v>
+        <v>1511585194250</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1079,14 +1079,14 @@
         <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-645000</v>
+        <v>-859000</v>
       </c>
       <c r="S7" t="n">
-        <v>53000</v>
+        <v>-5000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전반적으로 정치 관련 부정적 언급이 압도적이며, 특정 정치인에 대한 비난과 함께 경제 정책 실패 및 국민 피해를 주장하는 내용이 주를 이룸. 주가와 관련된 구체적인 팩트나 분석 없이 감정적인 비판에 집중.</t>
+          <t>정치적 이슈에 대한 부정적 언급만 다수 포함되어 있으며, 기업 분석이나 주가 전망에 대한 객관적 근거는 부재함. 외인 및 기관 매도세 언급과 함께 전 정부 정책 비판으로 일관.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16490</v>
+        <v>16480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-2.08%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>21924735260</v>
+        <v>22293513430</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1171,23 +1171,23 @@
         <v>16340</v>
       </c>
       <c r="R8" t="n">
-        <v>219000</v>
+        <v>349000</v>
       </c>
       <c r="S8" t="n">
-        <v>-36000</v>
+        <v>-60000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치 관련 부정적 언급이 다수 포함되었으며, 공매도 금지 및 정치인 탄핵 요구 등 강한 불만을 표출. 조선업 관련 수주 경쟁 탈락 뉴스 언급 및 주가 하락에 대한 우려.</t>
+          <t>중국발 선박 수주 쏠림으로 인한 한국 조선업체 탈락 뉴스 언급 및 주가 하락에 대한 부정적 전망이 지배적. 경영진 비판과 함께 주가 반등에 대한 근거 없는 기대만 일부 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '조선업', '실적']</t>
+          <t>['선박 수주', '주가 하락', '조선업']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F9" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G9" t="n">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>52781555700</v>
+        <v>53304453400</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1263,23 +1263,23 @@
         <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>-58000</v>
+        <v>-82000</v>
       </c>
       <c r="S9" t="n">
-        <v>-115000</v>
+        <v>-122000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치 관련 부정적 언급 및 기업에 대한 강한 불신 표현. 폴란드 원전에 이어 불가리아 원전 우선 공급자 체결 가능성 언급이 있으나, 전반적인 주가 하락 및 신용 문제에 대한 우려가 큼.</t>
+          <t>정치적 요인에 따른 주가 하락 언급이 다수이며, 재무 건전성에 대한 부정적 전망과 함께 회사가 망했다는 식의 극단적 표현이 나타남. 폴란드 및 불가리아 원전 공급자 체결 가능성 언급은 있으나, 주가 반등 근거로는 부족함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '주가', '신용']</t>
+          <t>['원전', '주가 하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>18597822440</v>
+        <v>18807408880</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1355,10 +1355,10 @@
         <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>49000</v>
+        <v>68000</v>
       </c>
       <c r="S10" t="n">
-        <v>-18000</v>
+        <v>-17000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27200</v>
+        <v>27100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.39%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>37691341050</v>
+        <v>38987645925</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1447,10 +1447,10 @@
         <v>22000</v>
       </c>
       <c r="R11" t="n">
-        <v>-267000</v>
+        <v>-243000</v>
       </c>
       <c r="S11" t="n">
-        <v>-36000</v>
+        <v>-85000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3080</v>
+        <v>3060</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.16%</t>
+          <t>'-19.69%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="F12" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G12" t="n">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>23393866973</v>
+        <v>23709114503</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1539,10 +1539,10 @@
         <v>2500</v>
       </c>
       <c r="R12" t="n">
-        <v>316000</v>
+        <v>120000</v>
       </c>
       <c r="S12" t="n">
-        <v>-86000</v>
+        <v>-142000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261026_13.xlsx
+++ b/data/trending_integrated_20261026_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F2" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G2" t="n">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58966480445</v>
+        <v>58980641605</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 언급과 함께 차세대 면역항암제 관련 긍정적 뉴스 및 빅파마와의 임상 진입 소식이 사실 기반으로 제시됨. 연기금 순매수 등 객관적 지표와 함께 주가 상승 기대감이 높음.</t>
+          <t>공매도 세력 청산 기대감 및 신규 투자 유치 소식 기반의 긍정적 전망. 차세대 면역항암제 개발 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['면역항암제', 'AI 신약', '공매도']</t>
+          <t>['공매도', '신규 투자', '면역항암제']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2080</v>
+        <v>2130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.00%</t>
+          <t>'+9.57%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>63736636547</v>
+        <v>64609146343</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5870</v>
+        <v>5750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.92%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>39860399160</v>
+        <v>40635743580</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급이 많으나, 특정 정치인 지지 및 당선 가능성 언급과 함께 주가 상승 기대감이 일부 나타남. 단기적인 주가 상승 전망만 존재하며, 객관적 근거는 부족함.</t>
+          <t>정치 테마주 관련 언급과 함께 주가 상승 기대감 표출. 특정 정치인 관련 소식에 민감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '주가 상승']</t>
+          <t>['정치 테마주', '주가 상승', '기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1287000</v>
+        <v>1286000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.78%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G5" t="n">
-        <v>1852</v>
+        <v>1879</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1985108567000</v>
+        <v>2019939937000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치 관련 부정적 언급과 함께, 특정 정치인에 대한 강한 비난과 함께 주가 하락에 대한 우려를 표출. 250 이상 목표가 언급이 있으나, 실적 발표 후 하락 가능성 및 다수의 물린 투자자 언급.</t>
+          <t>정치적 이슈와 반도체 업황에 대한 부정적 전망이 혼재. 실적 발표 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적 발표', '외인', '반도체']</t>
+          <t>['정치', '반도체', '실적']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59800</v>
+        <v>60000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F6" t="n">
         <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>691</v>
+        <v>706</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -969,7 +969,7 @@
         <v>59400</v>
       </c>
       <c r="L6" t="n">
-        <v>60200</v>
+        <v>60600</v>
       </c>
       <c r="M6" t="n">
         <v>57700</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>201993936550</v>
+        <v>220417697950</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G7" t="n">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1511585194250</v>
+        <v>1553054448000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 부정적 언급만 다수 포함되어 있으며, 기업 분석이나 주가 전망에 대한 객관적 근거는 부재함. 외인 및 기관 매도세 언급과 함께 전 정부 정책 비판으로 일관.</t>
+          <t>정치적 이슈에 대한 부정적 언급 다수. 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치', '주가', '불만']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16480</v>
+        <v>58200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="G8" t="n">
-        <v>198</v>
+        <v>544</v>
       </c>
       <c r="H8" t="n">
-        <v>27.94</v>
+        <v>22.23</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16830</v>
+        <v>59400</v>
       </c>
       <c r="K8" t="n">
-        <v>16520</v>
+        <v>58300</v>
       </c>
       <c r="L8" t="n">
-        <v>16820</v>
+        <v>59100</v>
       </c>
       <c r="M8" t="n">
-        <v>16340</v>
+        <v>57200</v>
       </c>
       <c r="N8" t="n">
-        <v>27.89</v>
+        <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>22293513430</v>
+        <v>54386555100</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>16340</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>349000</v>
+        <v>-82000</v>
       </c>
       <c r="S8" t="n">
-        <v>-60000</v>
+        <v>-122000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중국발 선박 수주 쏠림으로 인한 한국 조선업체 탈락 뉴스 언급 및 주가 하락에 대한 부정적 전망이 지배적. 경영진 비판과 함께 주가 반등에 대한 근거 없는 기대만 일부 존재.</t>
+          <t>정치적 요인에 따른 주가 하락 언급이 다수이며, 재무 건전성에 대한 부정적 전망과 함께 회사가 망했다는 식의 극단적 표현이 나타남. 폴란드 및 불가리아 원전 공급자 체결 가능성 언급은 있으나, 주가 반등 근거로는 부족함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['선박 수주', '주가 하락', '조선업']</t>
+          <t>['원전', '주가 하락']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58100</v>
+        <v>16470</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.19%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>542</v>
+        <v>203</v>
       </c>
       <c r="H9" t="n">
-        <v>22.23</v>
+        <v>27.94</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>59400</v>
+        <v>16830</v>
       </c>
       <c r="K9" t="n">
-        <v>58300</v>
+        <v>16520</v>
       </c>
       <c r="L9" t="n">
-        <v>59100</v>
+        <v>16820</v>
       </c>
       <c r="M9" t="n">
-        <v>57200</v>
+        <v>16340</v>
       </c>
       <c r="N9" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>53304453400</v>
+        <v>22811071125</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>16340</v>
       </c>
       <c r="R9" t="n">
-        <v>-82000</v>
+        <v>349000</v>
       </c>
       <c r="S9" t="n">
-        <v>-122000</v>
+        <v>-60000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 주가 하락 언급이 다수이며, 재무 건전성에 대한 부정적 전망과 함께 회사가 망했다는 식의 극단적 표현이 나타남. 폴란드 및 불가리아 원전 공급자 체결 가능성 언급은 있으나, 주가 반등 근거로는 부족함.</t>
+          <t>중국발 선박 수주 쏠림으로 인한 한국 조선업체 탈락 뉴스 언급 및 주가 하락에 대한 부정적 전망이 지배적. 경영진 비판과 함께 주가 반등에 대한 근거 없는 기대만 일부 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', '주가 하락']</t>
+          <t>['선박 수주', '주가 하락', '조선업']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14250</v>
+        <v>14260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-2.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>18807408880</v>
+        <v>19023865900</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
         <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>38987645925</v>
+        <v>40925487050</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F12" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G12" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>23709114503</v>
+        <v>23964379813</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_13.xlsx
+++ b/data/trending_integrated_20261026_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F2" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G2" t="n">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58980641605</v>
+        <v>58994464895</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 세력 청산 기대감 및 신규 투자 유치 소식 기반의 긍정적 전망. 차세대 면역항암제 개발 기대.</t>
+          <t>공매도 포지션 청산 및 숏 스퀴즈 가능성 언급. 신약 개발 뉴스 및 빅파마 협력에 따른 긍정적 전망 제시. AI 신약 밸류체인 합류 및 기술력 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '신규 투자', '면역항암제']</t>
+          <t>['공매도', 'AI 신약', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2130</v>
+        <v>2110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.57%</t>
+          <t>'+8.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>64609146343</v>
+        <v>65492224437</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5750</v>
+        <v>5710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
         <v>173</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>40635743580</v>
+        <v>40807587485</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1286000</v>
+        <v>1289000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="G5" t="n">
-        <v>1879</v>
+        <v>1905</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2019939937000</v>
+        <v>2048720106000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 업황에 대한 부정적 전망이 혼재. 실적 발표 및 주가 하락 우려.</t>
+          <t>정치적 이슈와 연계된 부정적 언급 다수. SK하이닉스 주가 관련 언급은 있으나, 구체적인 분석이나 근거 제시 미흡. 기대감과 우려 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '실적']</t>
+          <t>['정치', '반도체', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>60100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>706</v>
+        <v>780</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>220417697950</v>
+        <v>228653904150</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주주 외 인원 및 공매도 세력에 대한 부정적 언급과 함께, 20% 이상 상승 및 10만원 목표 등 강한 기대감을 표현. 외인 매수세 유입 가능성 언급.</t>
+          <t>공매도 및 비주주 대상 부정적 언급. 본격적인 호재 시작 전 기대감 표출. 외인 매수 및 자사주 보유에 따른 주가 방어 및 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기술적 분석', '수급동향', '유동성 장세']</t>
+          <t>['공매도', '호재', '외인매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214000</v>
+        <v>214500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="G7" t="n">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1553054448000</v>
+        <v>1584075692500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 부정적 언급 다수. 주가 하락에 대한 불만 표출.</t>
+          <t>전반적인 정치적 이슈와 현 정부에 대한 불만 표출. 특정 정치인 관련 부정적 언급 다수. 삼성전자 주가 관련 구체적 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정치', '주가', '불만']</t>
+          <t>['이재명', '정부', '주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>54386555100</v>
+        <v>55640667150</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16470</v>
+        <v>16460</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-2.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H9" t="n">
         <v>27.94</v>
@@ -1254,7 +1254,7 @@
         <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>22811071125</v>
+        <v>23281981875</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14260</v>
+        <v>14250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.99%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>19023865900</v>
+        <v>19220149105</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27100</v>
+        <v>27050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-4.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>40925487050</v>
+        <v>41796373475</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3060</v>
+        <v>3075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.69%</t>
+          <t>'-19.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G12" t="n">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>23964379813</v>
+        <v>24224438118</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>김정은 관련 이슈와 전쟁 가능성에 대한 언급이 있으며, 주가 급락에 대한 불안감이 나타남. 투기적 거래 가능성 제기.</t>
+          <t>북한 관련 테마주 논의 및 주가 급락에 대한 부정적 반응. 루머 및 감정적 표현 위주로, 객관적 근거 제시 부족. 테마주 투자 위험성 암시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['김정은', '전쟁 가능성', '주가 급락']</t>
+          <t>['북한', '테마주', '급락']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_13.xlsx
+++ b/data/trending_integrated_20261026_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F2" t="n">
         <v>112</v>
       </c>
       <c r="G2" t="n">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58994464895</v>
+        <v>58998827825</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 포지션 청산 및 숏 스퀴즈 가능성 언급. 신약 개발 뉴스 및 빅파마 협력에 따른 긍정적 전망 제시. AI 신약 밸류체인 합류 및 기술력 강조.</t>
+          <t>공매도 청산 기대감 및 글로벌 신약 개발 관련 긍정적 뉴스 기반 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', 'AI 신약', '숏스퀴즈']</t>
+          <t>['공매도', '신약', '임상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>65492224437</v>
+        <v>65847397182</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5710</v>
+        <v>5660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>40807587485</v>
+        <v>41392018565</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급과 함께 주가 상승 기대감 표출. 특정 정치인 관련 소식에 민감.</t>
+          <t>정치 테마주 관련 언급과 함께 주가 상승에 대한 기대감 표출. 일부 부정적 언급 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '주가 상승', '기대감']</t>
+          <t>['정치 테마', '우상향', '물려있습니다']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1289000</v>
+        <v>1290000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G5" t="n">
-        <v>1905</v>
+        <v>1875</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2048720106000</v>
+        <v>2085278390000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 언급 다수. SK하이닉스 주가 관련 언급은 있으나, 구체적인 분석이나 근거 제시 미흡. 기대감과 우려 혼재.</t>
+          <t>정치적 이슈와 연관된 부정적 언급이 다수. 주가 하락 및 반등에 대한 불확실성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '주가']</t>
+          <t>['이재명', '외인', '반도체']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60100</v>
+        <v>60000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.50%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F6" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G6" t="n">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>228653904150</v>
+        <v>234826613050</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214500</v>
+        <v>213750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'-0.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G7" t="n">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1584075692500</v>
+        <v>1614576772750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전반적인 정치적 이슈와 현 정부에 대한 불만 표출. 특정 정치인 관련 부정적 언급 다수. 삼성전자 주가 관련 구체적 근거 제시 부족.</t>
+          <t>정치적 이슈와 관련하여 부정적인 언급 다수. 주가 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명', '정부', '주가']</t>
+          <t>['이재명', '정부', '개미']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58200</v>
+        <v>58050</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-2.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G8" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>55640667150</v>
+        <v>56507591400</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16460</v>
+        <v>16420</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.20%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="H9" t="n">
         <v>27.94</v>
@@ -1254,7 +1254,7 @@
         <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>23281981875</v>
+        <v>23841170030</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>중국발 선박 수주 쏠림으로 인한 한국 조선업체 탈락 뉴스 언급 및 주가 하락에 대한 부정적 전망이 지배적. 경영진 비판과 함께 주가 반등에 대한 근거 없는 기대만 일부 존재.</t>
+          <t>국내 조선업의 경쟁력 약화와 관련된 부정적 뉴스 언급. 주가 하락 및 상장 폐지 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['선박 수주', '주가 하락', '조선업']</t>
+          <t>['조선', '수주', '실적']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14250</v>
+        <v>14220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>19220149105</v>
+        <v>19432537560</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27050</v>
+        <v>26950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-5.27%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>41796373475</v>
+        <v>42641281475</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3075</v>
+        <v>3065</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.29%</t>
+          <t>'-19.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F12" t="n">
         <v>140</v>
       </c>
       <c r="G12" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>24224438118</v>
+        <v>24351770689</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_13.xlsx
+++ b/data/trending_integrated_20261026_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58998827825</v>
+        <v>59015559735</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 청산 기대감 및 글로벌 신약 개발 관련 긍정적 뉴스 기반 주가 상승 전망.</t>
+          <t>글로벌 AI 신약 밸류체인 합류 및 빅파마와의 후기 임상 진입 소식 기반. 공매도 스퀴즈 및 리레이팅 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '신약', '임상']</t>
+          <t>['AI 신약', '빅파마', '공매도 스퀴즈']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2110</v>
+        <v>2100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.54%</t>
+          <t>'+8.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>65847397182</v>
+        <v>66214581844</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 및 신용/단타 투자자 퇴출 언급. 기술적 분석 기반 긍정적 흐름 기대.</t>
+          <t>국내 로봇 전시회 기대감 및 단기 차익 실현 가능성 언급. 변동성 높은 단타 매매 기조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '단타', '기술적 분석']</t>
+          <t>['로봇 전시회', '단타 매매', '변동성']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5660</v>
+        <v>5650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>41392018565</v>
+        <v>41600333525</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1290000</v>
+        <v>1293000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.02%</t>
+          <t>'+1.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G5" t="n">
-        <v>1875</v>
+        <v>1884</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>2085278390000</v>
+        <v>2128031858500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 부정적 언급이 다수. 주가 하락 및 반등에 대한 불확실성 제기.</t>
+          <t>이재명 정부 정책 비판과 함께 SK하이닉스 주가 하락에 대한 부정적 전망. 개인 투자자들의 고점 물림 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['이재명', '외인', '반도체']</t>
+          <t>['정부 정책', 'SK하이닉스', '주가 하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>60500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+1.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G6" t="n">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>234826613050</v>
+        <v>245262266350</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213750</v>
+        <v>214750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.81%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G7" t="n">
-        <v>1783</v>
+        <v>1861</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1614576772750</v>
+        <v>1663014215000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련하여 부정적인 언급 다수. 주가 하락 우려 제기.</t>
+          <t>이재명 정부 정책에 대한 부정적인 인식 확산. 외인 매도 및 주가 하락에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명', '정부', '개미']</t>
+          <t>['정부 정책', '외인 매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58050</v>
+        <v>58000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.27%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F8" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G8" t="n">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="H8" t="n">
         <v>22.23</v>
@@ -1162,7 +1162,7 @@
         <v>22.25</v>
       </c>
       <c r="O8" t="n">
-        <v>56507591400</v>
+        <v>58994134000</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 주가 하락 언급이 다수이며, 재무 건전성에 대한 부정적 전망과 함께 회사가 망했다는 식의 극단적 표현이 나타남. 폴란드 및 불가리아 원전 공급자 체결 가능성 언급은 있으나, 주가 반등 근거로는 부족함.</t>
+          <t>폴란드 원전에 이어 불가리아 원전 공급자 체결 가능성 언급에도 불구하고, 정부 정책 및 증시 전반에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '주가 하락']</t>
+          <t>['원전 수주', '정부 정책', '증시 붕괴']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16420</v>
+        <v>16430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H9" t="n">
         <v>27.94</v>
@@ -1254,7 +1254,7 @@
         <v>27.89</v>
       </c>
       <c r="O9" t="n">
-        <v>23841170030</v>
+        <v>24743093760</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1314,13 +1314,13 @@
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>19432537560</v>
+        <v>19917543220</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>42641281475</v>
+        <v>43624021525</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3065</v>
+        <v>3105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.55%</t>
+          <t>'-18.50%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G12" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>24351770689</v>
+        <v>24664195920</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
